--- a/docs/legal-acts/export/EU 2014-910.xlsx
+++ b/docs/legal-acts/export/EU 2014-910.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr"/>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -17352,7 +17352,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr"/>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -20603,7 +20603,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -20789,7 +20789,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -21254,7 +21254,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -21905,7 +21905,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -21998,7 +21998,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -22277,7 +22277,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -23951,7 +23951,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -24695,7 +24695,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -24788,7 +24788,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -24881,7 +24881,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -25067,7 +25067,7 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -25439,7 +25439,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -25625,7 +25625,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -26090,7 +26090,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -26183,7 +26183,7 @@
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -26276,7 +26276,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -26369,7 +26369,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -26741,7 +26741,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -26927,7 +26927,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -27113,7 +27113,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -27299,7 +27299,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -27485,7 +27485,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -27578,7 +27578,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -27857,7 +27857,7 @@
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -27950,7 +27950,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -28322,7 +28322,7 @@
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -28694,7 +28694,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -28787,7 +28787,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr"/>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -28969,7 +28969,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -29062,7 +29062,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -29155,7 +29155,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -29434,7 +29434,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr"/>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -29616,7 +29616,7 @@
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -29802,7 +29802,7 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -29895,7 +29895,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -30267,7 +30267,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -30453,7 +30453,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -30546,7 +30546,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -30825,7 +30825,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -31011,7 +31011,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -31383,7 +31383,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -31569,7 +31569,7 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -31755,7 +31755,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -31848,7 +31848,7 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -31941,7 +31941,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -32034,7 +32034,7 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -32313,7 +32313,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -32406,7 +32406,7 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -32499,7 +32499,7 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -32685,7 +32685,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -32778,7 +32778,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -32871,7 +32871,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -33057,7 +33057,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -33150,7 +33150,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -33243,7 +33243,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -33429,7 +33429,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -33708,7 +33708,7 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G389" s="3" t="inlineStr">
@@ -33801,7 +33801,7 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -34080,7 +34080,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -34266,7 +34266,7 @@
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -34452,7 +34452,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -34545,7 +34545,7 @@
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -34731,7 +34731,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -34824,7 +34824,7 @@
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -35010,7 +35010,7 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -35103,7 +35103,7 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -35289,7 +35289,7 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -35382,7 +35382,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -35661,7 +35661,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -35940,7 +35940,7 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -36033,7 +36033,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -36126,7 +36126,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -36219,7 +36219,7 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -36312,7 +36312,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -36405,7 +36405,7 @@
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -36498,7 +36498,7 @@
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
@@ -36591,7 +36591,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -36684,7 +36684,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -36870,7 +36870,7 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
@@ -37056,7 +37056,7 @@
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G425" s="3" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -37335,7 +37335,7 @@
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
@@ -37428,7 +37428,7 @@
       </c>
       <c r="F429" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -37521,7 +37521,7 @@
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
@@ -37614,7 +37614,7 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -37707,7 +37707,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -37800,7 +37800,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -37893,7 +37893,7 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
@@ -38079,7 +38079,7 @@
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -38265,7 +38265,7 @@
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
@@ -38358,7 +38358,7 @@
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
@@ -38544,7 +38544,7 @@
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -38637,7 +38637,7 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -38730,7 +38730,7 @@
       </c>
       <c r="F443" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr">
@@ -38823,7 +38823,7 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -38916,7 +38916,7 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
@@ -39009,7 +39009,7 @@
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr">
@@ -39102,7 +39102,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -39195,7 +39195,7 @@
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G449" s="3" t="inlineStr">
@@ -39381,7 +39381,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr">
@@ -39567,7 +39567,7 @@
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
@@ -39660,7 +39660,7 @@
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
@@ -39753,7 +39753,7 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -39846,7 +39846,7 @@
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G455" s="3" t="inlineStr">
@@ -39939,7 +39939,7 @@
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
@@ -40032,7 +40032,7 @@
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
@@ -40218,7 +40218,7 @@
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G459" s="3" t="inlineStr">
@@ -40311,7 +40311,7 @@
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -40404,7 +40404,7 @@
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -40497,7 +40497,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -40590,7 +40590,7 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
@@ -40776,7 +40776,7 @@
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
@@ -40962,7 +40962,7 @@
       </c>
       <c r="F467" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -41055,7 +41055,7 @@
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -41148,7 +41148,7 @@
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr">
@@ -41241,7 +41241,7 @@
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -41334,7 +41334,7 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -41427,7 +41427,7 @@
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -41520,7 +41520,7 @@
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr">
@@ -41613,7 +41613,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -41706,7 +41706,7 @@
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
@@ -41799,7 +41799,7 @@
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
@@ -41892,7 +41892,7 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G479" s="3" t="inlineStr">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
@@ -42264,7 +42264,7 @@
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G481" s="3" t="inlineStr"/>
@@ -42353,7 +42353,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr"/>
@@ -42442,7 +42442,7 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr"/>
@@ -42531,7 +42531,7 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -42624,7 +42624,7 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -42903,7 +42903,7 @@
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
@@ -42996,7 +42996,7 @@
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G489" s="3" t="inlineStr">
@@ -43089,7 +43089,7 @@
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
@@ -43182,7 +43182,7 @@
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
@@ -43368,7 +43368,7 @@
       </c>
       <c r="F493" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G493" s="3" t="inlineStr">
@@ -43461,7 +43461,7 @@
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -43647,7 +43647,7 @@
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
@@ -43740,7 +43740,7 @@
       </c>
       <c r="F497" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G497" s="3" t="inlineStr">
@@ -43833,7 +43833,7 @@
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
@@ -43926,7 +43926,7 @@
       </c>
       <c r="F499" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G499" s="3" t="inlineStr">
@@ -44019,7 +44019,7 @@
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
@@ -44112,7 +44112,7 @@
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
@@ -44205,7 +44205,7 @@
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
@@ -44298,7 +44298,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -44391,7 +44391,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -44484,7 +44484,7 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -44577,7 +44577,7 @@
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
@@ -44670,7 +44670,7 @@
       </c>
       <c r="F507" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G507" s="3" t="inlineStr">
@@ -44763,7 +44763,7 @@
       </c>
       <c r="F508" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G508" s="3" t="inlineStr">
@@ -44856,7 +44856,7 @@
       </c>
       <c r="F509" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G509" s="3" t="inlineStr">
@@ -44949,7 +44949,7 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -45042,7 +45042,7 @@
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G511" s="3" t="inlineStr">
@@ -45135,7 +45135,7 @@
       </c>
       <c r="F512" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G512" s="3" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -45321,7 +45321,7 @@
       </c>
       <c r="F514" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G514" s="3" t="inlineStr"/>
@@ -45410,7 +45410,7 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
@@ -45503,7 +45503,7 @@
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
@@ -45596,7 +45596,7 @@
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G517" s="3" t="inlineStr">
@@ -45689,7 +45689,7 @@
       </c>
       <c r="F518" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G518" s="3" t="inlineStr">
@@ -45782,7 +45782,7 @@
       </c>
       <c r="F519" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G519" s="3" t="inlineStr">
@@ -45875,7 +45875,7 @@
       </c>
       <c r="F520" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G520" s="3" t="inlineStr">
@@ -45968,7 +45968,7 @@
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
@@ -46061,7 +46061,7 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="F523" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G523" s="3" t="inlineStr">
@@ -46247,7 +46247,7 @@
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -46340,7 +46340,7 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="F526" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G526" s="3" t="inlineStr">
@@ -46526,7 +46526,7 @@
       </c>
       <c r="F527" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G527" s="3" t="inlineStr">
@@ -46619,7 +46619,7 @@
       </c>
       <c r="F528" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G528" s="3" t="inlineStr">
@@ -46712,7 +46712,7 @@
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G529" s="3" t="inlineStr">
@@ -46805,7 +46805,7 @@
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
@@ -46898,7 +46898,7 @@
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
@@ -46991,7 +46991,7 @@
       </c>
       <c r="F532" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G532" s="3" t="inlineStr">
@@ -47084,7 +47084,7 @@
       </c>
       <c r="F533" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G533" s="3" t="inlineStr">
@@ -47177,7 +47177,7 @@
       </c>
       <c r="F534" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G534" s="3" t="inlineStr">
@@ -47270,7 +47270,7 @@
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G535" s="3" t="inlineStr">
@@ -47363,7 +47363,7 @@
       </c>
       <c r="F536" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G536" s="3" t="inlineStr">
@@ -47456,7 +47456,7 @@
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
@@ -47549,7 +47549,7 @@
       </c>
       <c r="F538" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G538" s="3" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="F539" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G539" s="3" t="inlineStr">
@@ -47735,7 +47735,7 @@
       </c>
       <c r="F540" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G540" s="3" t="inlineStr">
@@ -47828,7 +47828,7 @@
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G541" s="3" t="inlineStr">
@@ -47921,7 +47921,7 @@
       </c>
       <c r="F542" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
@@ -48014,7 +48014,7 @@
       </c>
       <c r="F543" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G543" s="3" t="inlineStr">
@@ -48107,7 +48107,7 @@
       </c>
       <c r="F544" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G544" s="3" t="inlineStr">
@@ -48200,7 +48200,7 @@
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
@@ -48293,7 +48293,7 @@
       </c>
       <c r="F546" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
@@ -48386,7 +48386,7 @@
       </c>
       <c r="F547" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G547" s="3" t="inlineStr">
@@ -48479,7 +48479,7 @@
       </c>
       <c r="F548" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G548" s="3" t="inlineStr">
@@ -48572,7 +48572,7 @@
       </c>
       <c r="F549" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G549" s="3" t="inlineStr">
@@ -48665,7 +48665,7 @@
       </c>
       <c r="F550" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G550" s="3" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="F551" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G551" s="3" t="inlineStr"/>
@@ -48847,7 +48847,7 @@
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
@@ -48940,7 +48940,7 @@
       </c>
       <c r="F553" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G553" s="3" t="inlineStr">
@@ -49033,7 +49033,7 @@
       </c>
       <c r="F554" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G554" s="3" t="inlineStr">
@@ -49126,7 +49126,7 @@
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
@@ -49219,7 +49219,7 @@
       </c>
       <c r="F556" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
@@ -49312,7 +49312,7 @@
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
@@ -49405,7 +49405,7 @@
       </c>
       <c r="F558" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G558" s="3" t="inlineStr">
@@ -49498,7 +49498,7 @@
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G559" s="3" t="inlineStr">
@@ -49591,7 +49591,7 @@
       </c>
       <c r="F560" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G560" s="3" t="inlineStr">
@@ -49684,7 +49684,7 @@
       </c>
       <c r="F561" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G561" s="3" t="inlineStr">
@@ -49777,7 +49777,7 @@
       </c>
       <c r="F562" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G562" s="3" t="inlineStr">
@@ -49870,7 +49870,7 @@
       </c>
       <c r="F563" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
@@ -49963,7 +49963,7 @@
       </c>
       <c r="F564" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G564" s="3" t="inlineStr">
@@ -50056,7 +50056,7 @@
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G565" s="3" t="inlineStr">
@@ -50149,7 +50149,7 @@
       </c>
       <c r="F566" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G566" s="3" t="inlineStr">
@@ -50242,7 +50242,7 @@
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
@@ -50335,7 +50335,7 @@
       </c>
       <c r="F568" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G568" s="3" t="inlineStr">
@@ -50428,7 +50428,7 @@
       </c>
       <c r="F569" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G569" s="3" t="inlineStr">
@@ -50521,7 +50521,7 @@
       </c>
       <c r="F570" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G570" s="3" t="inlineStr">
@@ -50614,7 +50614,7 @@
       </c>
       <c r="F571" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G571" s="3" t="inlineStr">
@@ -50707,7 +50707,7 @@
       </c>
       <c r="F572" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G572" s="3" t="inlineStr">
@@ -50800,7 +50800,7 @@
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
@@ -50893,7 +50893,7 @@
       </c>
       <c r="F574" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G574" s="3" t="inlineStr">
@@ -50986,7 +50986,7 @@
       </c>
       <c r="F575" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G575" s="3" t="inlineStr">
@@ -51079,7 +51079,7 @@
       </c>
       <c r="F576" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G576" s="3" t="inlineStr">
@@ -51172,7 +51172,7 @@
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G577" s="3" t="inlineStr">
@@ -51265,7 +51265,7 @@
       </c>
       <c r="F578" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G578" s="3" t="inlineStr">
@@ -51358,7 +51358,7 @@
       </c>
       <c r="F579" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G579" s="3" t="inlineStr">
@@ -51451,7 +51451,7 @@
       </c>
       <c r="F580" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G580" s="3" t="inlineStr">
@@ -51544,7 +51544,7 @@
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
@@ -51637,7 +51637,7 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -51730,7 +51730,7 @@
       </c>
       <c r="F583" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G583" s="3" t="inlineStr">
@@ -51823,7 +51823,7 @@
       </c>
       <c r="F584" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G584" s="3" t="inlineStr">
@@ -51916,7 +51916,7 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
@@ -52009,7 +52009,7 @@
       </c>
       <c r="F586" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G586" s="3" t="inlineStr">
@@ -52102,7 +52102,7 @@
       </c>
       <c r="F587" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
@@ -52195,7 +52195,7 @@
       </c>
       <c r="F588" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G588" s="3" t="inlineStr">
@@ -52288,7 +52288,7 @@
       </c>
       <c r="F589" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G589" s="3" t="inlineStr">
@@ -52381,7 +52381,7 @@
       </c>
       <c r="F590" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G590" s="3" t="inlineStr">
@@ -52474,7 +52474,7 @@
       </c>
       <c r="F591" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G591" s="3" t="inlineStr">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="F592" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G592" s="3" t="inlineStr">
@@ -52660,7 +52660,7 @@
       </c>
       <c r="F593" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G593" s="3" t="inlineStr">
@@ -52753,7 +52753,7 @@
       </c>
       <c r="F594" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G594" s="3" t="inlineStr">
@@ -52846,7 +52846,7 @@
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G595" s="3" t="inlineStr">
@@ -52939,7 +52939,7 @@
       </c>
       <c r="F596" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G596" s="3" t="inlineStr">
@@ -53032,7 +53032,7 @@
       </c>
       <c r="F597" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G597" s="3" t="inlineStr">
@@ -53125,7 +53125,7 @@
       </c>
       <c r="F598" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G598" s="3" t="inlineStr">
@@ -53218,7 +53218,7 @@
       </c>
       <c r="F599" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G599" s="3" t="inlineStr">
@@ -53311,7 +53311,7 @@
       </c>
       <c r="F600" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G600" s="3" t="inlineStr">
@@ -53404,7 +53404,7 @@
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G601" s="3" t="inlineStr">
@@ -53497,7 +53497,7 @@
       </c>
       <c r="F602" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G602" s="3" t="inlineStr">
@@ -53590,7 +53590,7 @@
       </c>
       <c r="F603" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G603" s="3" t="inlineStr">
@@ -53683,7 +53683,7 @@
       </c>
       <c r="F604" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G604" s="3" t="inlineStr">
